--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/14.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/14.xlsx
@@ -426,13 +426,13 @@
         <v>-19.47339437419893</v>
       </c>
       <c r="E2">
-        <v>-38.43249302988979</v>
+        <v>-38.23110499805768</v>
       </c>
       <c r="F2">
-        <v>-6.514248684770916</v>
+        <v>-6.535625547217517</v>
       </c>
       <c r="G2">
-        <v>-23.39548081269409</v>
+        <v>-24.62535510162441</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-18.5975833755092</v>
       </c>
       <c r="E3">
-        <v>-38.62139153040875</v>
+        <v>-37.782598139627</v>
       </c>
       <c r="F3">
-        <v>-6.288257413976017</v>
+        <v>-7.014765081918793</v>
       </c>
       <c r="G3">
-        <v>-23.65471804696502</v>
+        <v>-24.3378838797218</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-17.66929850309647</v>
       </c>
       <c r="E4">
-        <v>-38.45343722217527</v>
+        <v>-39.40236762929757</v>
       </c>
       <c r="F4">
-        <v>-6.380363374459102</v>
+        <v>-6.755461349045583</v>
       </c>
       <c r="G4">
-        <v>-23.56373928972754</v>
+        <v>-24.19586644190537</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-16.75596597090948</v>
       </c>
       <c r="E5">
-        <v>-38.60459994878831</v>
+        <v>-38.54428293924315</v>
       </c>
       <c r="F5">
-        <v>-6.397948844944141</v>
+        <v>-6.816172715313954</v>
       </c>
       <c r="G5">
-        <v>-23.5504242755686</v>
+        <v>-23.66119512931261</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-15.87578330212789</v>
       </c>
       <c r="E6">
-        <v>-39.02226789922676</v>
+        <v>-39.59485947394162</v>
       </c>
       <c r="F6">
-        <v>-6.285090793998095</v>
+        <v>-6.982227447959611</v>
       </c>
       <c r="G6">
-        <v>-23.16257896818805</v>
+        <v>-24.60727124661614</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-15.05658649803893</v>
       </c>
       <c r="E7">
-        <v>-39.41190912403174</v>
+        <v>-39.99904389302223</v>
       </c>
       <c r="F7">
-        <v>-6.324500523850848</v>
+        <v>-6.96821917321107</v>
       </c>
       <c r="G7">
-        <v>-23.32555215926806</v>
+        <v>-23.87266781254294</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-14.32838354242347</v>
       </c>
       <c r="E8">
-        <v>-39.55802260212622</v>
+        <v>-39.72989404037634</v>
       </c>
       <c r="F8">
-        <v>-6.538823445387268</v>
+        <v>-6.749100790162699</v>
       </c>
       <c r="G8">
-        <v>-22.95551262107048</v>
+        <v>-23.65526759752454</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-13.71384537496731</v>
       </c>
       <c r="E9">
-        <v>-39.86565542688929</v>
+        <v>-40.33945381265281</v>
       </c>
       <c r="F9">
-        <v>-6.457470452143538</v>
+        <v>-6.797237927388959</v>
       </c>
       <c r="G9">
-        <v>-22.68744616184631</v>
+        <v>-22.78701412948543</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-13.22157953019705</v>
       </c>
       <c r="E10">
-        <v>-40.36138068379795</v>
+        <v>-40.59267249373972</v>
       </c>
       <c r="F10">
-        <v>-6.456681370671171</v>
+        <v>-6.79701224929601</v>
       </c>
       <c r="G10">
-        <v>-22.13198793381246</v>
+        <v>-23.58986942566901</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-12.85182044447885</v>
       </c>
       <c r="E11">
-        <v>-40.51627260875631</v>
+        <v>-41.25753399059786</v>
       </c>
       <c r="F11">
-        <v>-6.306468052371176</v>
+        <v>-6.751061418086013</v>
       </c>
       <c r="G11">
-        <v>-22.1575470006484</v>
+        <v>-23.84859187010859</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-12.60502354016336</v>
       </c>
       <c r="E12">
-        <v>-41.22211000267286</v>
+        <v>-41.81406080377052</v>
       </c>
       <c r="F12">
-        <v>-6.417304502716163</v>
+        <v>-6.549682124996479</v>
       </c>
       <c r="G12">
-        <v>-21.969671886022</v>
+        <v>-22.53085404729324</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-12.46551630444425</v>
       </c>
       <c r="E13">
-        <v>-41.12657957924405</v>
+        <v>-42.10972487173131</v>
       </c>
       <c r="F13">
-        <v>-6.221056416792654</v>
+        <v>-6.542231976443773</v>
       </c>
       <c r="G13">
-        <v>-21.78461735619505</v>
+        <v>-22.27224250612922</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-12.42859107294283</v>
       </c>
       <c r="E14">
-        <v>-41.24956840481838</v>
+        <v>-41.55869336176697</v>
       </c>
       <c r="F14">
-        <v>-6.211338005442559</v>
+        <v>-6.676407896791071</v>
       </c>
       <c r="G14">
-        <v>-21.36662787640666</v>
+        <v>-22.53711925472631</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-12.47356028019817</v>
       </c>
       <c r="E15">
-        <v>-41.63989342919851</v>
+        <v>-42.40890303552207</v>
       </c>
       <c r="F15">
-        <v>-6.259433966315019</v>
+        <v>-6.355651227354584</v>
       </c>
       <c r="G15">
-        <v>-21.49812108995375</v>
+        <v>-21.82544465905811</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-12.5748583023148</v>
       </c>
       <c r="E16">
-        <v>-42.42173220238579</v>
+        <v>-42.4127024252145</v>
       </c>
       <c r="F16">
-        <v>-6.148009565148924</v>
+        <v>-6.32616341506206</v>
       </c>
       <c r="G16">
-        <v>-21.16404069740373</v>
+        <v>-21.91491877334799</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-12.70310082797286</v>
       </c>
       <c r="E17">
-        <v>-43.2192327029286</v>
+        <v>-43.33364233449539</v>
       </c>
       <c r="F17">
-        <v>-6.108049497490556</v>
+        <v>-6.433218371607457</v>
       </c>
       <c r="G17">
-        <v>-20.92275489631949</v>
+        <v>-22.0586378315716</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-12.83908499484687</v>
       </c>
       <c r="E18">
-        <v>-43.19195770398041</v>
+        <v>-42.9165404433079</v>
       </c>
       <c r="F18">
-        <v>-6.106015623168653</v>
+        <v>-5.896029284355184</v>
       </c>
       <c r="G18">
-        <v>-20.59633345087459</v>
+        <v>-21.91810848397508</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-12.95977749355907</v>
       </c>
       <c r="E19">
-        <v>-43.81067178646339</v>
+        <v>-44.46750882737994</v>
       </c>
       <c r="F19">
-        <v>-5.808474102820115</v>
+        <v>-5.667451425873893</v>
       </c>
       <c r="G19">
-        <v>-20.56348787330671</v>
+        <v>-21.20248771802406</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-13.05782344100721</v>
       </c>
       <c r="E20">
-        <v>-44.05394141015544</v>
+        <v>-43.774428144743</v>
       </c>
       <c r="F20">
-        <v>-5.913974256083029</v>
+        <v>-5.380639909028937</v>
       </c>
       <c r="G20">
-        <v>-20.48453301746786</v>
+        <v>-22.20698503245911</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-13.12226096354841</v>
       </c>
       <c r="E21">
-        <v>-44.67269172043048</v>
+        <v>-44.78036977538487</v>
       </c>
       <c r="F21">
-        <v>-5.61666910384237</v>
+        <v>-5.615428270257623</v>
       </c>
       <c r="G21">
-        <v>-20.67586599691003</v>
+        <v>-21.2501248130614</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-13.14449387303286</v>
       </c>
       <c r="E22">
-        <v>-44.3423214276749</v>
+        <v>-45.06571345108218</v>
       </c>
       <c r="F22">
-        <v>-5.485231806949346</v>
+        <v>-5.412884161467284</v>
       </c>
       <c r="G22">
-        <v>-20.63733621265123</v>
+        <v>-20.83064227723481</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-13.11778306365744</v>
       </c>
       <c r="E23">
-        <v>-44.55234525943964</v>
+        <v>-44.96137288147145</v>
       </c>
       <c r="F23">
-        <v>-5.362163603966462</v>
+        <v>-5.262722709536019</v>
       </c>
       <c r="G23">
-        <v>-20.31254190033887</v>
+        <v>-21.28947892315949</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-13.0444312560666</v>
       </c>
       <c r="E24">
-        <v>-45.37372440342489</v>
+        <v>-44.40173047818153</v>
       </c>
       <c r="F24">
-        <v>-5.266108672783229</v>
+        <v>-5.136666845343659</v>
       </c>
       <c r="G24">
-        <v>-20.60956404612228</v>
+        <v>-21.03464802500132</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-12.92330420840536</v>
       </c>
       <c r="E25">
-        <v>-45.33672903501923</v>
+        <v>-45.45943709520508</v>
       </c>
       <c r="F25">
-        <v>-5.078748344457165</v>
+        <v>-5.48749809011434</v>
       </c>
       <c r="G25">
-        <v>-20.09374132455736</v>
+        <v>-21.72914916568456</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-12.76270656903325</v>
       </c>
       <c r="E26">
-        <v>-45.48179190714394</v>
+        <v>-45.98097691819446</v>
       </c>
       <c r="F26">
-        <v>-5.028861608120822</v>
+        <v>-5.312157297833504</v>
       </c>
       <c r="G26">
-        <v>-20.33695717369099</v>
+        <v>-21.33629831344863</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-12.56409156598677</v>
       </c>
       <c r="E27">
-        <v>-45.19492213570604</v>
+        <v>-45.88242826683954</v>
       </c>
       <c r="F27">
-        <v>-5.093810971418909</v>
+        <v>-5.303061282908177</v>
       </c>
       <c r="G27">
-        <v>-20.5943918159158</v>
+        <v>-21.77735401928188</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-12.32659948939482</v>
       </c>
       <c r="E28">
-        <v>-45.07562854492198</v>
+        <v>-45.15105027951973</v>
       </c>
       <c r="F28">
-        <v>-4.822350316012307</v>
+        <v>-5.346121454896019</v>
       </c>
       <c r="G28">
-        <v>-20.50803954606945</v>
+        <v>-21.4896957515563</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-12.04864445769651</v>
       </c>
       <c r="E29">
-        <v>-45.3209473031025</v>
+        <v>-45.18454287328046</v>
       </c>
       <c r="F29">
-        <v>-5.043224237067943</v>
+        <v>-5.189751083923274</v>
       </c>
       <c r="G29">
-        <v>-20.61555613354836</v>
+        <v>-21.59584011790918</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-11.73290596824159</v>
       </c>
       <c r="E30">
-        <v>-44.87021469969704</v>
+        <v>-46.42956981763129</v>
       </c>
       <c r="F30">
-        <v>-4.909846900428506</v>
+        <v>-5.092210636591358</v>
       </c>
       <c r="G30">
-        <v>-20.69219857332803</v>
+        <v>-21.06211893188619</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-11.3797363318336</v>
       </c>
       <c r="E31">
-        <v>-44.39865564433032</v>
+        <v>-45.22516554936627</v>
       </c>
       <c r="F31">
-        <v>-4.947619870217652</v>
+        <v>-5.30287282190424</v>
       </c>
       <c r="G31">
-        <v>-20.7712941273523</v>
+        <v>-22.16730979944371</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-10.99939880831162</v>
       </c>
       <c r="E32">
-        <v>-44.75666094971771</v>
+        <v>-44.71304495231283</v>
       </c>
       <c r="F32">
-        <v>-5.078768932634066</v>
+        <v>-5.081697996724671</v>
       </c>
       <c r="G32">
-        <v>-20.42954982187887</v>
+        <v>-21.90027954097333</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-10.59755143548231</v>
       </c>
       <c r="E33">
-        <v>-44.54392909049638</v>
+        <v>-44.26811785258521</v>
       </c>
       <c r="F33">
-        <v>-4.927308049999183</v>
+        <v>-5.234980933015266</v>
       </c>
       <c r="G33">
-        <v>-20.74997090353385</v>
+        <v>-21.93992663435164</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-10.17914141014061</v>
       </c>
       <c r="E34">
-        <v>-44.3905609970416</v>
+        <v>-44.76447030314394</v>
       </c>
       <c r="F34">
-        <v>-5.088099336034877</v>
+        <v>-4.984237526541485</v>
       </c>
       <c r="G34">
-        <v>-20.82501434981805</v>
+        <v>-21.29235247668758</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.750046510235087</v>
       </c>
       <c r="E35">
-        <v>-43.71576629244763</v>
+        <v>-44.27324182092489</v>
       </c>
       <c r="F35">
-        <v>-4.999767346748285</v>
+        <v>-5.493899429424546</v>
       </c>
       <c r="G35">
-        <v>-20.76465317300052</v>
+        <v>-22.55955151130041</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.318693614894611</v>
       </c>
       <c r="E36">
-        <v>-43.66053475921309</v>
+        <v>-43.80783016902357</v>
       </c>
       <c r="F36">
-        <v>-4.99887651217085</v>
+        <v>-5.258820458160376</v>
       </c>
       <c r="G36">
-        <v>-21.12675898881323</v>
+        <v>-21.42361891786522</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-8.892177168297703</v>
       </c>
       <c r="E37">
-        <v>-43.24800662677334</v>
+        <v>-44.11006052429549</v>
       </c>
       <c r="F37">
-        <v>-5.080242570988382</v>
+        <v>-5.291509731960963</v>
       </c>
       <c r="G37">
-        <v>-21.07815521447842</v>
+        <v>-21.80179412172555</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-8.483947990206072</v>
       </c>
       <c r="E38">
-        <v>-42.72170737760189</v>
+        <v>-44.10255005015377</v>
       </c>
       <c r="F38">
-        <v>-5.240383745745788</v>
+        <v>-5.455875442247803</v>
       </c>
       <c r="G38">
-        <v>-20.75399321636407</v>
+        <v>-22.69559838023676</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-8.101200418104217</v>
       </c>
       <c r="E39">
-        <v>-42.86547737039741</v>
+        <v>-43.29807796387615</v>
       </c>
       <c r="F39">
-        <v>-5.049751480998427</v>
+        <v>-5.119035447387072</v>
       </c>
       <c r="G39">
-        <v>-21.18565524922964</v>
+        <v>-21.44299885145211</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.747858084050928</v>
       </c>
       <c r="E40">
-        <v>-42.40330584164858</v>
+        <v>-42.327392767621</v>
       </c>
       <c r="F40">
-        <v>-5.016108024383788</v>
+        <v>-5.105032319682756</v>
       </c>
       <c r="G40">
-        <v>-21.02463031419948</v>
+        <v>-22.10644210915867</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-7.426968122123747</v>
       </c>
       <c r="E41">
-        <v>-42.2237767538515</v>
+        <v>-42.49306472495461</v>
       </c>
       <c r="F41">
-        <v>-4.930940279516244</v>
+        <v>-5.355378215971762</v>
       </c>
       <c r="G41">
-        <v>-21.19467483055138</v>
+        <v>-22.50454514189265</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-7.141821830448524</v>
       </c>
       <c r="E42">
-        <v>-41.97519523014844</v>
+        <v>-42.27162234597954</v>
       </c>
       <c r="F42">
-        <v>-4.903485153766185</v>
+        <v>-5.330841860223859</v>
       </c>
       <c r="G42">
-        <v>-21.2744109751375</v>
+        <v>-21.90942823357111</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.894357054680483</v>
       </c>
       <c r="E43">
-        <v>-41.45365767139606</v>
+        <v>-42.52888042588128</v>
       </c>
       <c r="F43">
-        <v>-5.021829953856272</v>
+        <v>-5.181136515596241</v>
       </c>
       <c r="G43">
-        <v>-21.31823597698637</v>
+        <v>-22.31346541918423</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.690126323567229</v>
       </c>
       <c r="E44">
-        <v>-40.93581308319693</v>
+        <v>-41.35057148908545</v>
       </c>
       <c r="F44">
-        <v>-5.103124745907609</v>
+        <v>-5.506947582461852</v>
       </c>
       <c r="G44">
-        <v>-21.42406087569471</v>
+        <v>-21.96520927063506</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.528909589116831</v>
       </c>
       <c r="E45">
-        <v>-40.5954371271214</v>
+        <v>-41.11660335100516</v>
       </c>
       <c r="F45">
-        <v>-4.986290801260853</v>
+        <v>-5.664987971322428</v>
       </c>
       <c r="G45">
-        <v>-21.29819393429162</v>
+        <v>-21.95439040781272</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.407216133051497</v>
       </c>
       <c r="E46">
-        <v>-40.55282192247222</v>
+        <v>-41.02499232182998</v>
       </c>
       <c r="F46">
-        <v>-5.159324925875851</v>
+        <v>-5.54237587564319</v>
       </c>
       <c r="G46">
-        <v>-21.23716568254792</v>
+        <v>-21.65312083210242</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.321603666017406</v>
       </c>
       <c r="E47">
-        <v>-39.81509275035665</v>
+        <v>-40.43977989005575</v>
       </c>
       <c r="F47">
-        <v>-5.207486214617322</v>
+        <v>-5.427158894736097</v>
       </c>
       <c r="G47">
-        <v>-21.02850696302597</v>
+        <v>-21.66657654444679</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.269328082816467</v>
       </c>
       <c r="E48">
-        <v>-39.79402628927297</v>
+        <v>-40.70948448076758</v>
       </c>
       <c r="F48">
-        <v>-5.263489223199092</v>
+        <v>-5.462427233619976</v>
       </c>
       <c r="G48">
-        <v>-21.5138892183573</v>
+        <v>-21.98233141216417</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.247856434165279</v>
       </c>
       <c r="E49">
-        <v>-38.92485815908476</v>
+        <v>-39.86189000075191</v>
       </c>
       <c r="F49">
-        <v>-5.160168249275823</v>
+        <v>-5.412599094402505</v>
       </c>
       <c r="G49">
-        <v>-21.43020193767006</v>
+        <v>-21.5491101123496</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.257132734220692</v>
       </c>
       <c r="E50">
-        <v>-39.09510161092913</v>
+        <v>-40.05456072011926</v>
       </c>
       <c r="F50">
-        <v>-5.150816465845153</v>
+        <v>-5.375506326304039</v>
       </c>
       <c r="G50">
-        <v>-21.13854784147858</v>
+        <v>-21.98079697430672</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.293698818016416</v>
       </c>
       <c r="E51">
-        <v>-38.90943870508865</v>
+        <v>-39.48366053044627</v>
       </c>
       <c r="F51">
-        <v>-5.270109113925629</v>
+        <v>-5.462740015538275</v>
       </c>
       <c r="G51">
-        <v>-21.5336829701366</v>
+        <v>-22.07726958186662</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.351608670390986</v>
       </c>
       <c r="E52">
-        <v>-38.56735098583822</v>
+        <v>-39.62510288760184</v>
       </c>
       <c r="F52">
-        <v>-5.13820145637572</v>
+        <v>-5.673436250528339</v>
       </c>
       <c r="G52">
-        <v>-21.37413288314419</v>
+        <v>-22.13031610831513</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.426772286417769</v>
       </c>
       <c r="E53">
-        <v>-38.38470630792385</v>
+        <v>-39.31225099654493</v>
       </c>
       <c r="F53">
-        <v>-5.126560426044282</v>
+        <v>-5.752798921362841</v>
       </c>
       <c r="G53">
-        <v>-21.63026813624483</v>
+        <v>-21.94614549414716</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.515918511860414</v>
       </c>
       <c r="E54">
-        <v>-37.53055459754508</v>
+        <v>-38.46649281273938</v>
       </c>
       <c r="F54">
-        <v>-5.082943581427164</v>
+        <v>-5.515575612289166</v>
       </c>
       <c r="G54">
-        <v>-21.49729676411447</v>
+        <v>-21.70863040443215</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.616539419318967</v>
       </c>
       <c r="E55">
-        <v>-37.23326027894153</v>
+        <v>-38.902559953071</v>
       </c>
       <c r="F55">
-        <v>-5.19533285542224</v>
+        <v>-5.756556263647221</v>
       </c>
       <c r="G55">
-        <v>-21.85811808825794</v>
+        <v>-21.9946499521158</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.727916674106722</v>
       </c>
       <c r="E56">
-        <v>-37.05575541902586</v>
+        <v>-38.26187597893981</v>
       </c>
       <c r="F56">
-        <v>-5.353222000367891</v>
+        <v>-5.645178977732111</v>
       </c>
       <c r="G56">
-        <v>-21.48045932950173</v>
+        <v>-22.51968757718928</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.846932474915913</v>
       </c>
       <c r="E57">
-        <v>-36.88218127454887</v>
+        <v>-38.08997510560864</v>
       </c>
       <c r="F57">
-        <v>-5.359284426612193</v>
+        <v>-5.94633174349433</v>
       </c>
       <c r="G57">
-        <v>-21.70752302694927</v>
+        <v>-22.05129173101996</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.967720704568272</v>
       </c>
       <c r="E58">
-        <v>-36.89233637751106</v>
+        <v>-37.59937381703965</v>
       </c>
       <c r="F58">
-        <v>-5.447005105415426</v>
+        <v>-5.863512634499382</v>
       </c>
       <c r="G58">
-        <v>-21.59881795362176</v>
+        <v>-21.93049157956472</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.087430352981028</v>
       </c>
       <c r="E59">
-        <v>-36.48501599018014</v>
+        <v>-37.38527888714201</v>
       </c>
       <c r="F59">
-        <v>-5.417286863912206</v>
+        <v>-5.920252066331831</v>
       </c>
       <c r="G59">
-        <v>-21.75436393578441</v>
+        <v>-22.27581789531164</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.203849640698186</v>
       </c>
       <c r="E60">
-        <v>-36.38567938434789</v>
+        <v>-36.83445115850802</v>
       </c>
       <c r="F60">
-        <v>-5.437876624518833</v>
+        <v>-5.713678217839655</v>
       </c>
       <c r="G60">
-        <v>-21.87492076214252</v>
+        <v>-21.68012991788457</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.316195594892427</v>
       </c>
       <c r="E61">
-        <v>-36.03213915433206</v>
+        <v>-36.37910856856276</v>
       </c>
       <c r="F61">
-        <v>-5.413974542990064</v>
+        <v>-5.859952463601473</v>
       </c>
       <c r="G61">
-        <v>-21.78391386526795</v>
+        <v>-21.95762812135013</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.425214520218931</v>
       </c>
       <c r="E62">
-        <v>-35.94287613892987</v>
+        <v>-37.40778540296014</v>
       </c>
       <c r="F62">
-        <v>-5.634504799862049</v>
+        <v>-6.140913374868319</v>
       </c>
       <c r="G62">
-        <v>-21.92454749504896</v>
+        <v>-22.4533492104006</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.529916462529388</v>
       </c>
       <c r="E63">
-        <v>-35.50514478440044</v>
+        <v>-37.35180440727731</v>
       </c>
       <c r="F63">
-        <v>-5.477310901813276</v>
+        <v>-5.935979057925103</v>
       </c>
       <c r="G63">
-        <v>-21.72120220111753</v>
+        <v>-22.7649973463765</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.626443679852036</v>
       </c>
       <c r="E64">
-        <v>-35.7500174878912</v>
+        <v>-36.45396197967255</v>
       </c>
       <c r="F64">
-        <v>-5.613782799811482</v>
+        <v>-6.215718536004665</v>
       </c>
       <c r="G64">
-        <v>-21.95904006902262</v>
+        <v>-22.14632756181581</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.714926829784876</v>
       </c>
       <c r="E65">
-        <v>-35.24859314644389</v>
+        <v>-36.09971983618553</v>
       </c>
       <c r="F65">
-        <v>-5.708113867105759</v>
+        <v>-6.011406219559737</v>
       </c>
       <c r="G65">
-        <v>-22.15989417743575</v>
+        <v>-22.05155160884479</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.795089686032281</v>
       </c>
       <c r="E66">
-        <v>-35.97275501043247</v>
+        <v>-36.45634395700058</v>
       </c>
       <c r="F66">
-        <v>-5.825669981649956</v>
+        <v>-6.084702504885148</v>
       </c>
       <c r="G66">
-        <v>-21.79081966326287</v>
+        <v>-22.21721130762992</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.868698355442168</v>
       </c>
       <c r="E67">
-        <v>-35.23909240797579</v>
+        <v>-36.49171360323749</v>
       </c>
       <c r="F67">
-        <v>-5.709281850218396</v>
+        <v>-6.170859274096885</v>
       </c>
       <c r="G67">
-        <v>-21.97081899005135</v>
+        <v>-22.05083818628108</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.938370291040225</v>
       </c>
       <c r="E68">
-        <v>-35.24346238539319</v>
+        <v>-36.95648447606672</v>
       </c>
       <c r="F68">
-        <v>-5.621747256860226</v>
+        <v>-6.308800851184618</v>
       </c>
       <c r="G68">
-        <v>-21.83975614742437</v>
+        <v>-22.4903197277104</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.00496026388978</v>
       </c>
       <c r="E69">
-        <v>-35.4489781212833</v>
+        <v>-36.29093691539641</v>
       </c>
       <c r="F69">
-        <v>-5.780718072946123</v>
+        <v>-6.155174646636851</v>
       </c>
       <c r="G69">
-        <v>-22.07873780881328</v>
+        <v>-22.64807218847499</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.065413557731649</v>
       </c>
       <c r="E70">
-        <v>-34.94201092765059</v>
+        <v>-37.5185179136327</v>
       </c>
       <c r="F70">
-        <v>-5.902744989289605</v>
+        <v>-6.263067383611515</v>
       </c>
       <c r="G70">
-        <v>-21.98637358826762</v>
+        <v>-23.01223550834036</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.121016357354124</v>
       </c>
       <c r="E71">
-        <v>-35.36150158887713</v>
+        <v>-36.83592744103452</v>
       </c>
       <c r="F71">
-        <v>-5.936584825437758</v>
+        <v>-6.292312888898978</v>
       </c>
       <c r="G71">
-        <v>-21.81680247992784</v>
+        <v>-22.60636593577125</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.171420226771913</v>
       </c>
       <c r="E72">
-        <v>-35.18924523033636</v>
+        <v>-36.98217224487523</v>
       </c>
       <c r="F72">
-        <v>-6.060181986196398</v>
+        <v>-6.268938181440049</v>
       </c>
       <c r="G72">
-        <v>-21.57390940898428</v>
+        <v>-22.54075257845566</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.218817671768063</v>
       </c>
       <c r="E73">
-        <v>-36.23719298587338</v>
+        <v>-36.53152115400191</v>
       </c>
       <c r="F73">
-        <v>-6.112191284385909</v>
+        <v>-6.383821000398985</v>
       </c>
       <c r="G73">
-        <v>-21.48296210192942</v>
+        <v>-23.04510260445424</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.264986899592396</v>
       </c>
       <c r="E74">
-        <v>-36.00873147218641</v>
+        <v>-37.21585282485604</v>
       </c>
       <c r="F74">
-        <v>-5.996741894635726</v>
+        <v>-6.459019316528838</v>
       </c>
       <c r="G74">
-        <v>-22.04420716356591</v>
+        <v>-22.63423079757529</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.309257705472714</v>
       </c>
       <c r="E75">
-        <v>-36.19423135296261</v>
+        <v>-37.73048898922074</v>
       </c>
       <c r="F75">
-        <v>-6.076118818823466</v>
+        <v>-6.32379141952721</v>
       </c>
       <c r="G75">
-        <v>-21.51446856382667</v>
+        <v>-22.13499059861658</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.346454775035037</v>
       </c>
       <c r="E76">
-        <v>-36.76552551987427</v>
+        <v>-37.47515324653525</v>
       </c>
       <c r="F76">
-        <v>-6.058151675212805</v>
+        <v>-6.736667510947063</v>
       </c>
       <c r="G76">
-        <v>-21.49349294728984</v>
+        <v>-22.5980117741029</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.376277914444456</v>
       </c>
       <c r="E77">
-        <v>-36.37893422231346</v>
+        <v>-37.64745715405309</v>
       </c>
       <c r="F77">
-        <v>-6.347170878103885</v>
+        <v>-6.444253634426238</v>
       </c>
       <c r="G77">
-        <v>-21.35669955033439</v>
+        <v>-22.2652986368606</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.395803075390482</v>
       </c>
       <c r="E78">
-        <v>-36.47490617195802</v>
+        <v>-37.65072218381263</v>
       </c>
       <c r="F78">
-        <v>-6.351435006281205</v>
+        <v>-6.440508961789182</v>
       </c>
       <c r="G78">
-        <v>-21.15359096040902</v>
+        <v>-22.66778648716135</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.40563326212115</v>
       </c>
       <c r="E79">
-        <v>-36.56827424904817</v>
+        <v>-38.30156352514302</v>
       </c>
       <c r="F79">
-        <v>-6.345931232298574</v>
+        <v>-6.290362555064115</v>
       </c>
       <c r="G79">
-        <v>-21.06735290438378</v>
+        <v>-22.6137385206872</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.405029836611003</v>
       </c>
       <c r="E80">
-        <v>-37.5319810668575</v>
+        <v>-38.28904908722283</v>
       </c>
       <c r="F80">
-        <v>-6.290069569469758</v>
+        <v>-6.346546897973202</v>
       </c>
       <c r="G80">
-        <v>-21.00436812022637</v>
+        <v>-21.87886031133425</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-8.391130480123117</v>
       </c>
       <c r="E81">
-        <v>-37.41323315719136</v>
+        <v>-38.54981899871752</v>
       </c>
       <c r="F81">
-        <v>-6.228487956800853</v>
+        <v>-6.648594457577644</v>
       </c>
       <c r="G81">
-        <v>-20.75801718446705</v>
+        <v>-22.56308717393636</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.357608518370009</v>
       </c>
       <c r="E82">
-        <v>-38.24112424679965</v>
+        <v>-38.70317803522428</v>
       </c>
       <c r="F82">
-        <v>-6.404157368059143</v>
+        <v>-6.496845736392631</v>
       </c>
       <c r="G82">
-        <v>-20.88879697545042</v>
+        <v>-21.66716416628001</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-8.30361549360917</v>
       </c>
       <c r="E83">
-        <v>-38.55961408799611</v>
+        <v>-39.80577994355988</v>
       </c>
       <c r="F83">
-        <v>-6.400516824086027</v>
+        <v>-6.696020510847872</v>
       </c>
       <c r="G83">
-        <v>-20.62154159988336</v>
+        <v>-22.09731824565245</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.225294768665607</v>
       </c>
       <c r="E84">
-        <v>-38.68448223028361</v>
+        <v>-40.14364259656115</v>
       </c>
       <c r="F84">
-        <v>-6.429471323411526</v>
+        <v>-6.96876436397246</v>
       </c>
       <c r="G84">
-        <v>-21.06524077632972</v>
+        <v>-21.78292566742448</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.123987613975954</v>
       </c>
       <c r="E85">
-        <v>-39.83972991319538</v>
+        <v>-40.24887074707738</v>
       </c>
       <c r="F85">
-        <v>-6.45456672734758</v>
+        <v>-6.648634446152009</v>
       </c>
       <c r="G85">
-        <v>-20.63145171795517</v>
+        <v>-21.66473588112695</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.999665284398874</v>
       </c>
       <c r="E86">
-        <v>-40.34045913388252</v>
+        <v>-41.61522003856772</v>
       </c>
       <c r="F86">
-        <v>-6.614148062063879</v>
+        <v>-6.639986224074273</v>
       </c>
       <c r="G86">
-        <v>-20.78723109357835</v>
+        <v>-21.14065169316878</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.850933046709279</v>
       </c>
       <c r="E87">
-        <v>-40.48439215174231</v>
+        <v>-42.53649279068817</v>
       </c>
       <c r="F87">
-        <v>-6.656337195798228</v>
+        <v>-6.685646841175266</v>
       </c>
       <c r="G87">
-        <v>-20.37541578122071</v>
+        <v>-21.76431709094823</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.674213823764713</v>
       </c>
       <c r="E88">
-        <v>-40.92077402101746</v>
+        <v>-43.46303215807955</v>
       </c>
       <c r="F88">
-        <v>-6.448794911138761</v>
+        <v>-6.82532415994632</v>
       </c>
       <c r="G88">
-        <v>-20.91466226774875</v>
+        <v>-21.83728648045208</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.470462480490512</v>
       </c>
       <c r="E89">
-        <v>-42.28680858356426</v>
+        <v>-43.08901190436404</v>
       </c>
       <c r="F89">
-        <v>-6.639590693521892</v>
+        <v>-6.873072101443863</v>
       </c>
       <c r="G89">
-        <v>-20.41113822286221</v>
+        <v>-22.34062182424287</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.2371486850055</v>
       </c>
       <c r="E90">
-        <v>-43.26595749773975</v>
+        <v>-44.00551843759142</v>
       </c>
       <c r="F90">
-        <v>-6.60882047536434</v>
+        <v>-7.083502273840133</v>
       </c>
       <c r="G90">
-        <v>-20.94000614912463</v>
+        <v>-21.72421479755827</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.977699495767003</v>
       </c>
       <c r="E91">
-        <v>-44.14677286307568</v>
+        <v>-45.09568968477596</v>
       </c>
       <c r="F91">
-        <v>-6.710532404077523</v>
+        <v>-6.939428983374296</v>
       </c>
       <c r="G91">
-        <v>-20.53647382170625</v>
+        <v>-22.0003954038992</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.693898196288426</v>
       </c>
       <c r="E92">
-        <v>-44.83453711722762</v>
+        <v>-46.12268645531649</v>
       </c>
       <c r="F92">
-        <v>-6.57130564963941</v>
+        <v>-6.963203972503353</v>
       </c>
       <c r="G92">
-        <v>-20.72387718359332</v>
+        <v>-21.41360120706338</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.387089771148463</v>
       </c>
       <c r="E93">
-        <v>-45.92304641445134</v>
+        <v>-46.88644529602815</v>
       </c>
       <c r="F93">
-        <v>-6.640983562874521</v>
+        <v>-6.905751477082476</v>
       </c>
       <c r="G93">
-        <v>-20.83617916464924</v>
+        <v>-22.11432617336045</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.057833160309677</v>
       </c>
       <c r="E94">
-        <v>-46.5818329634282</v>
+        <v>-48.48864091019346</v>
       </c>
       <c r="F94">
-        <v>-6.712740486050125</v>
+        <v>-7.016256536964658</v>
       </c>
       <c r="G94">
-        <v>-20.82454921816978</v>
+        <v>-21.77940490224346</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.710870165708798</v>
       </c>
       <c r="E95">
-        <v>-47.58972183789336</v>
+        <v>-49.00913352356857</v>
       </c>
       <c r="F95">
-        <v>-6.779545556754628</v>
+        <v>-6.849721149573665</v>
       </c>
       <c r="G95">
-        <v>-20.97694852679736</v>
+        <v>-22.23158900690698</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.346855081468476</v>
       </c>
       <c r="E96">
-        <v>-48.13397195803122</v>
+        <v>-50.3766613504194</v>
       </c>
       <c r="F96">
-        <v>-6.79679686529151</v>
+        <v>-7.2989967418275</v>
       </c>
       <c r="G96">
-        <v>-21.07777450174141</v>
+        <v>-21.27043832049037</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.975166561097018</v>
       </c>
       <c r="E97">
-        <v>-49.67824386116442</v>
+        <v>-51.37881151619835</v>
       </c>
       <c r="F97">
-        <v>-6.862854426803926</v>
+        <v>-7.172068651602211</v>
       </c>
       <c r="G97">
-        <v>-20.9137485571799</v>
+        <v>-22.15680212790207</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.598140766047317</v>
       </c>
       <c r="E98">
-        <v>-51.18429431155437</v>
+        <v>-51.53475631136349</v>
       </c>
       <c r="F98">
-        <v>-6.87388533443144</v>
+        <v>-7.002287458937524</v>
       </c>
       <c r="G98">
-        <v>-21.33673530545981</v>
+        <v>-21.91281161111224</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.223576143694046</v>
       </c>
       <c r="E99">
-        <v>-52.48507469576914</v>
+        <v>-53.59699393937552</v>
       </c>
       <c r="F99">
-        <v>-6.950365660499842</v>
+        <v>-6.979444084813226</v>
       </c>
       <c r="G99">
-        <v>-21.2463689991471</v>
+        <v>-22.31249377406845</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.847421791871745</v>
       </c>
       <c r="E100">
-        <v>-53.74898990520597</v>
+        <v>-54.91958458652973</v>
       </c>
       <c r="F100">
-        <v>-7.119432205870186</v>
+        <v>-7.110129121396416</v>
       </c>
       <c r="G100">
-        <v>-21.46048846353608</v>
+        <v>-22.65733509489387</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.484456625772811</v>
       </c>
       <c r="E101">
-        <v>-54.87192692607301</v>
+        <v>-56.36292699309848</v>
       </c>
       <c r="F101">
-        <v>-7.041552279699014</v>
+        <v>-7.411139353626245</v>
       </c>
       <c r="G101">
-        <v>-21.61465394820886</v>
+        <v>-22.03360183093086</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.119476186488073</v>
       </c>
       <c r="E102">
-        <v>-55.89464315655779</v>
+        <v>-57.29993619239558</v>
       </c>
       <c r="F102">
-        <v>-7.223643222517933</v>
+        <v>-7.171069333169569</v>
       </c>
       <c r="G102">
-        <v>-21.28260126480165</v>
+        <v>-23.3321898030743</v>
       </c>
     </row>
   </sheetData>
